--- a/Excel/Exercise 5.xlsx
+++ b/Excel/Exercise 5.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Brinton/Personal/School/Aerodynamics/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FA7142-60B4-3C43-B5A2-231C0CB37880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CFAC72-25DA-8E43-9472-5D51B0F1FB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="680" windowWidth="28040" windowHeight="17080" xr2:uid="{DE84619F-1E04-6947-AE41-8D81EAA25096}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17980" xr2:uid="{DE84619F-1E04-6947-AE41-8D81EAA25096}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$C$3:$C$13</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$D$3:$D$13</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$J$3:$J$13</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$K$3:$K$13</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$G$5:$G$7</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0000001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
@@ -46,7 +47,7 @@
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -155,10 +156,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="167" formatCode="0.000000"/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="174" formatCode="0.0000000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -197,13 +198,13 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -982,7 +983,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -2242,121 +2243,11 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
+          <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$B$3:$B$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>-0.17453292519943295</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.13962634015954636</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.10471975511965978</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-6.9813170079773182E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-3.4906585039886591E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.4906585039886591E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.9813170079773182E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.10471975511965978</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.13962634015954636</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.17453292519943295</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$3:$C$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>-0.86229999999999996</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.65129999999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.43140000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.2077</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.7100000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.24210000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.46510000000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.67669999999999997</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.9113</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.1086</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.3059000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredSeriesTitle>
-                <c15:tx>
-                  <c:v>CL XFOIL</c:v>
-                </c15:tx>
-              </c15:filteredSeriesTitle>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0BE9-294F-89B6-989B42C55A80}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="1"/>
+          <c:tx>
+            <c:v>CD XFOIL</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -2371,47 +2262,114 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$13</c:f>
+              <c:f>Sheet1!$C$3:$C$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>-0.17453292519943295</c:v>
+                  <c:v>-0.86229999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.13962634015954636</c:v>
+                  <c:v>-0.65129999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.10471975511965978</c:v>
+                  <c:v>-0.43140000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-6.9813170079773182E-2</c:v>
+                  <c:v>-0.2077</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.4906585039886591E-2</c:v>
+                  <c:v>1.7100000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.24210000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.4906585039886591E-2</c:v>
+                  <c:v>0.46510000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.9813170079773182E-2</c:v>
+                  <c:v>0.67669999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.10471975511965978</c:v>
+                  <c:v>0.9113</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.13962634015954636</c:v>
+                  <c:v>1.1086</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.17453292519943295</c:v>
+                  <c:v>1.3059000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.0460000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5699999999999995E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.2700000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.4099999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.8399999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4799999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.11E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.7299999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.9000000000000008E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0030000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2290000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CBB6-D141-81BF-88715727108B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>CD EQ</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
             <c:numRef>
               <c:f>Sheet1!$J$3:$J$13</c:f>
               <c:numCache>
@@ -2452,18 +2410,53 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$3:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.076055943987681E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.676587411334466E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.0855990659446045E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.9875944037072262E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.3825734246223328E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.2705361286899234E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.6514825159099972E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.525412586282555E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.8923263398075968E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.7522237764851236E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2105104896315132E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:filteredSeriesTitle>
-                <c15:tx>
-                  <c:v>CL TAT</c:v>
-                </c15:tx>
-              </c15:filteredSeriesTitle>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0BE9-294F-89B6-989B42C55A80}"/>
+              <c16:uniqueId val="{00000001-CBB6-D141-81BF-88715727108B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2476,11 +2469,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="935262895"/>
-        <c:axId val="935243263"/>
+        <c:axId val="530900192"/>
+        <c:axId val="1475120160"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="935262895"/>
+        <c:axId val="530900192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2500,160 +2493,52 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-                  <a:lnSpc>
-                    <a:spcPct val="100000"/>
-                  </a:lnSpc>
-                  <a:spcBef>
-                    <a:spcPts val="0"/>
-                  </a:spcBef>
-                  <a:spcAft>
-                    <a:spcPts val="0"/>
-                  </a:spcAft>
-                  <a:buClrTx/>
-                  <a:buSzTx/>
-                  <a:buFontTx/>
-                  <a:buNone/>
-                  <a:tabLst/>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:effectLst/>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>C̃</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="-25000">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:effectLst/>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>L</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:endParaRPr>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-                <a:lnSpc>
-                  <a:spcPct val="100000"/>
-                </a:lnSpc>
-                <a:spcBef>
-                  <a:spcPts val="0"/>
-                </a:spcBef>
-                <a:spcAft>
-                  <a:spcPts val="0"/>
-                </a:spcAft>
-                <a:buClrTx/>
-                <a:buSzTx/>
-                <a:buFontTx/>
-                <a:buNone/>
-                <a:tabLst/>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="#,##0.000" sourceLinked="0"/>
-        <c:majorTickMark val="cross"/>
-        <c:minorTickMark val="out"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="935243263"/>
-        <c:crossesAt val="-1.5"/>
+        <c:crossAx val="1475120160"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="935243263"/>
+        <c:axId val="1475120160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2673,101 +2558,18 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:effectLst/>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>C̃</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="-25000">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:effectLst/>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>D</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US" sz="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:endParaRPr>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
-        <c:majorTickMark val="cross"/>
-        <c:minorTickMark val="out"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2778,35 +2580,25 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="935262895"/>
-        <c:crossesAt val="1"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossAx val="530900192"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2814,24 +2606,7 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -5811,28 +5586,26 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>196850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>196832</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>138690</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17A1F6E8-7230-DF49-980E-A57E2A21B292}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABE7ADE5-67D1-5B9A-97A0-9487AABD25D7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5847,19 +5620,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="0015"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6191,30 +5951,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="J1" s="1" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="J1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="Q1" s="1" t="s">
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="Q1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -6292,14 +6052,14 @@
       <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>-3.7244011751697399E-2</v>
       </c>
-      <c r="J3" s="4">
-        <f>G$2*(B3-G$3)</f>
+      <c r="J3" s="3">
+        <f t="shared" ref="J3:J13" si="0">G$2*(B3-G$3)</f>
         <v>-0.86260454545368925</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <f>G$5+(G$6*J3)+(G$7*J3^2)</f>
         <v>1.076055943987681E-2</v>
       </c>
@@ -6318,13 +6078,13 @@
         <f>(E3-L3)^2</f>
         <v>0</v>
       </c>
-      <c r="P3" s="4"/>
+      <c r="P3" s="3"/>
       <c r="Q3">
-        <f>U$2*(SIN(B3)-TAN(U$3)*COS(B3))</f>
+        <f t="shared" ref="Q3:Q13" si="1">U$2*(SIN(B3)-TAN(U$3)*COS(B3))</f>
         <v>-0.86313031380438598</v>
       </c>
       <c r="R3">
-        <f>(C3-Q3)^2</f>
+        <f t="shared" ref="R3:R13" si="2">(C3-Q3)^2</f>
         <v>6.8942101375400111E-7</v>
       </c>
       <c r="S3">
@@ -6334,7 +6094,7 @@
       <c r="T3" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="2">
+      <c r="U3" s="1">
         <v>-3.7323463916006425E-2</v>
       </c>
     </row>
@@ -6344,7 +6104,7 @@
         <v>-8</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B13" si="0">RADIANS(A4)</f>
+        <f t="shared" ref="B4:B13" si="3">RADIANS(A4)</f>
         <v>-0.13962634015954636</v>
       </c>
       <c r="C4">
@@ -6359,45 +6119,45 @@
       <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="4">
-        <f>G$2*(B4-G$3)</f>
+      <c r="J4" s="3">
+        <f t="shared" si="0"/>
         <v>-0.64328181818092445</v>
       </c>
-      <c r="K4" s="3">
-        <f t="shared" ref="K4:K13" si="1">G$5+(G$6*J4)+(G$7*J4^2)</f>
+      <c r="K4" s="2">
+        <f>G$5+(G$6*J4)+(G$7*J4^2)</f>
         <v>8.676587411334466E-3</v>
       </c>
       <c r="L4">
         <v>-5.4100000000000002E-2</v>
       </c>
       <c r="M4">
-        <f>(C4-J4)^2</f>
+        <f t="shared" ref="M4:M13" si="4">(C4-J4)^2</f>
         <v>6.4291239683753583E-5</v>
       </c>
       <c r="N4">
-        <f t="shared" ref="N4:N13" si="2">(D4-K4)^2</f>
+        <f t="shared" ref="N4:N13" si="5">(D4-K4)^2</f>
         <v>1.1360876254982755E-8</v>
       </c>
       <c r="O4">
-        <f>(E4-L4)^2</f>
+        <f t="shared" ref="O4:O13" si="6">(E4-L4)^2</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>U$2*(SIN(B4)-TAN(U$3)*COS(B4))</f>
+        <f t="shared" si="1"/>
         <v>-0.64444506688239123</v>
       </c>
       <c r="R4">
-        <f>(C4-Q4)^2</f>
+        <f t="shared" si="2"/>
         <v>4.6990108046889404E-5</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f t="shared" ref="A5:A13" si="3">A4+2</f>
+        <f t="shared" ref="A5:A13" si="7">A4+2</f>
         <v>-6</v>
       </c>
       <c r="B5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.10471975511965978</v>
       </c>
       <c r="C5">
@@ -6415,45 +6175,45 @@
       <c r="G5">
         <v>5.4076866340265171E-3</v>
       </c>
-      <c r="J5" s="4">
-        <f>G$2*(B5-G$3)</f>
+      <c r="J5" s="3">
+        <f t="shared" si="0"/>
         <v>-0.4239590909081597</v>
       </c>
-      <c r="K5" s="3">
-        <f t="shared" si="1"/>
+      <c r="K5" s="2">
+        <f t="shared" ref="K4:K13" si="8">G$5+(G$6*J5)+(G$7*J5^2)</f>
         <v>7.0855990659446045E-3</v>
       </c>
       <c r="L5">
         <v>-5.2999999999999999E-2</v>
       </c>
       <c r="M5">
-        <f>(C5-J5)^2</f>
+        <f t="shared" si="4"/>
         <v>5.5367128113031767E-5</v>
       </c>
       <c r="N5">
+        <f t="shared" si="5"/>
+        <v>3.4003704480502464E-8</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="1"/>
+        <v>-0.42497466291555275</v>
+      </c>
+      <c r="R5">
         <f t="shared" si="2"/>
-        <v>3.4003704480502464E-8</v>
-      </c>
-      <c r="O5">
-        <f>(E5-L5)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <f>U$2*(SIN(B5)-TAN(U$3)*COS(B5))</f>
-        <v>-0.42497466291555275</v>
-      </c>
-      <c r="R5">
-        <f>(C5-Q5)^2</f>
         <v>4.1284956648773192E-5</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6">
+        <f t="shared" si="7"/>
+        <v>-4</v>
+      </c>
+      <c r="B6">
         <f t="shared" si="3"/>
-        <v>-4</v>
-      </c>
-      <c r="B6">
-        <f t="shared" si="0"/>
         <v>-6.9813170079773182E-2</v>
       </c>
       <c r="C6">
@@ -6471,45 +6231,45 @@
       <c r="G6">
         <v>-1.7852252921561865E-3</v>
       </c>
-      <c r="J6" s="4">
-        <f>G$2*(B6-G$3)</f>
+      <c r="J6" s="3">
+        <f t="shared" si="0"/>
         <v>-0.20463636363539475</v>
       </c>
-      <c r="K6" s="3">
-        <f t="shared" si="1"/>
+      <c r="K6" s="2">
+        <f t="shared" si="8"/>
         <v>5.9875944037072262E-3</v>
       </c>
       <c r="L6">
         <v>-5.2600000000000001E-2</v>
       </c>
       <c r="M6">
-        <f>(C6-J6)^2</f>
+        <f t="shared" si="4"/>
         <v>9.3858677745316322E-6</v>
       </c>
       <c r="N6">
+        <f t="shared" si="5"/>
+        <v>1.784264877794537E-7</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="1"/>
+        <v>-0.20498649278428027</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="2"/>
-        <v>1.784264877794537E-7</v>
-      </c>
-      <c r="O6">
-        <f>(E6-L6)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <f>U$2*(SIN(B6)-TAN(U$3)*COS(B6))</f>
-        <v>-0.20498649278428027</v>
-      </c>
-      <c r="R6">
-        <f>(C6-Q6)^2</f>
         <v>7.3631214097630072E-6</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7">
+        <f t="shared" si="7"/>
+        <v>-2</v>
+      </c>
+      <c r="B7">
         <f t="shared" si="3"/>
-        <v>-2</v>
-      </c>
-      <c r="B7">
-        <f t="shared" si="0"/>
         <v>-3.4906585039886591E-2</v>
       </c>
       <c r="C7">
@@ -6527,47 +6287,47 @@
       <c r="G7">
         <v>5.1243085747845031E-3</v>
       </c>
-      <c r="J7" s="4">
-        <f>G$2*(B7-G$3)</f>
+      <c r="J7" s="3">
+        <f t="shared" si="0"/>
         <v>1.4686363637370097E-2</v>
       </c>
-      <c r="K7" s="3">
-        <f t="shared" si="1"/>
+      <c r="K7" s="2">
+        <f t="shared" si="8"/>
         <v>5.3825734246223328E-3</v>
       </c>
       <c r="L7">
         <v>-5.2499999999999998E-2</v>
       </c>
       <c r="M7">
-        <f>(C7-J7)^2</f>
+        <f t="shared" si="4"/>
         <v>5.8256404910093125E-6</v>
       </c>
       <c r="N7">
+        <f t="shared" si="5"/>
+        <v>2.0923907186174036E-7</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="1"/>
+        <v>1.5251421812701347E-2</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="2"/>
-        <v>2.0923907186174036E-7</v>
-      </c>
-      <c r="O7">
-        <f>(E7-L7)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <f>U$2*(SIN(B7)-TAN(U$3)*COS(B7))</f>
-        <v>1.5251421812701347E-2</v>
-      </c>
-      <c r="R7">
-        <f>(C7-Q7)^2</f>
         <v>3.4172413145563776E-6</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="B8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="B8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="C8">
         <v>0.24210000000000001</v>
       </c>
@@ -6580,49 +6340,49 @@
       <c r="F8" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <f>SQRT(AVERAGE(M3:M13))</f>
         <v>1.1066543653270915E-2</v>
       </c>
-      <c r="J8" s="4">
-        <f>G$2*(B8-G$3)</f>
+      <c r="J8" s="3">
+        <f t="shared" si="0"/>
         <v>0.23400909091013494</v>
       </c>
-      <c r="K8" s="3">
-        <f t="shared" si="1"/>
+      <c r="K8" s="2">
+        <f t="shared" si="8"/>
         <v>5.2705361286899234E-3</v>
       </c>
       <c r="L8">
         <v>-5.2699999999999997E-2</v>
       </c>
       <c r="M8">
-        <f>(C8-J8)^2</f>
+        <f t="shared" si="4"/>
         <v>6.5462809900461167E-5</v>
       </c>
       <c r="N8">
+        <f t="shared" si="5"/>
+        <v>4.3875113384204153E-8</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="1"/>
+        <v>0.23547075490150557</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="2"/>
-        <v>4.3875113384204153E-8</v>
-      </c>
-      <c r="O8">
-        <f>(E8-L8)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <f>U$2*(SIN(B8)-TAN(U$3)*COS(B8))</f>
-        <v>0.23547075490150557</v>
-      </c>
-      <c r="R8">
-        <f>(C8-Q8)^2</f>
         <v>4.3946890575912565E-5</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="B9">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <f t="shared" si="0"/>
         <v>3.4906585039886591E-2</v>
       </c>
       <c r="C9">
@@ -6637,49 +6397,49 @@
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <f>SQRT(AVERAGE(N3:N13))</f>
         <v>3.8192460499309432E-4</v>
       </c>
-      <c r="J9" s="4">
-        <f>G$2*(B9-G$3)</f>
+      <c r="J9" s="3">
+        <f t="shared" si="0"/>
         <v>0.4533318181828998</v>
       </c>
-      <c r="K9" s="3">
-        <f t="shared" si="1"/>
+      <c r="K9" s="2">
+        <f t="shared" si="8"/>
         <v>5.6514825159099972E-3</v>
       </c>
       <c r="L9">
         <v>-5.2600000000000001E-2</v>
       </c>
       <c r="M9">
-        <f>(C9-J9)^2</f>
+        <f t="shared" si="4"/>
         <v>1.3849010328032799E-4</v>
       </c>
       <c r="N9">
+        <f t="shared" si="5"/>
+        <v>2.9320331503622041E-7</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="1"/>
+        <v>0.45540320314695149</v>
+      </c>
+      <c r="R9">
         <f t="shared" si="2"/>
-        <v>2.9320331503622041E-7</v>
-      </c>
-      <c r="O9">
-        <f>(E9-L9)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <f>U$2*(SIN(B9)-TAN(U$3)*COS(B9))</f>
-        <v>0.45540320314695149</v>
-      </c>
-      <c r="R9">
-        <f>(C9-Q9)^2</f>
         <v>9.4027869209291836E-5</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="B10">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="B10">
-        <f t="shared" si="0"/>
         <v>6.9813170079773182E-2</v>
       </c>
       <c r="C10">
@@ -6698,45 +6458,45 @@
         <f>SQRT(AVERAGE(O3:O13))</f>
         <v>0</v>
       </c>
-      <c r="J10" s="4">
-        <f>G$2*(B10-G$3)</f>
+      <c r="J10" s="3">
+        <f t="shared" si="0"/>
         <v>0.67265454545566472</v>
       </c>
-      <c r="K10" s="3">
-        <f t="shared" si="1"/>
+      <c r="K10" s="2">
+        <f t="shared" si="8"/>
         <v>6.525412586282555E-3</v>
       </c>
       <c r="L10">
         <v>-4.9500000000000002E-2</v>
       </c>
       <c r="M10">
-        <f>(C10-J10)^2</f>
+        <f t="shared" si="4"/>
         <v>1.6365702470282705E-5</v>
       </c>
       <c r="N10">
+        <f t="shared" si="5"/>
+        <v>6.3268118241670328E-7</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="1"/>
+        <v>0.67478081273884871</v>
+      </c>
+      <c r="R10">
         <f t="shared" si="2"/>
-        <v>6.3268118241670328E-7</v>
-      </c>
-      <c r="O10">
-        <f>(E10-L10)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <f>U$2*(SIN(B10)-TAN(U$3)*COS(B10))</f>
-        <v>0.67478081273884871</v>
-      </c>
-      <c r="R10">
-        <f>(C10-Q10)^2</f>
         <v>3.6832797433652599E-6</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="B11">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <f t="shared" si="0"/>
         <v>0.10471975511965978</v>
       </c>
       <c r="C11">
@@ -6748,45 +6508,45 @@
       <c r="E11">
         <v>-5.2999999999999999E-2</v>
       </c>
-      <c r="J11" s="4">
-        <f>G$2*(B11-G$3)</f>
+      <c r="J11" s="3">
+        <f t="shared" si="0"/>
         <v>0.89197727272842953</v>
       </c>
-      <c r="K11" s="3">
-        <f t="shared" si="1"/>
+      <c r="K11" s="2">
+        <f t="shared" si="8"/>
         <v>7.8923263398075968E-3</v>
       </c>
       <c r="L11">
         <v>-5.2999999999999999E-2</v>
       </c>
       <c r="M11">
-        <f>(C11-J11)^2</f>
+        <f t="shared" si="4"/>
         <v>3.7336778921149329E-4</v>
       </c>
       <c r="N11">
+        <f t="shared" si="5"/>
+        <v>5.8885060748484647E-11</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="1"/>
+        <v>0.89333630585243973</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="2"/>
-        <v>5.8885060748484647E-11</v>
-      </c>
-      <c r="O11">
-        <f>(E11-L11)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <f>U$2*(SIN(B11)-TAN(U$3)*COS(B11))</f>
-        <v>0.89333630585243973</v>
-      </c>
-      <c r="R11">
-        <f>(C11-Q11)^2</f>
         <v>3.2269430742709116E-4</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="B12">
         <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="B12">
-        <f t="shared" si="0"/>
         <v>0.13962634015954636</v>
       </c>
       <c r="C12">
@@ -6798,45 +6558,45 @@
       <c r="E12">
         <v>-4.8399999999999999E-2</v>
       </c>
-      <c r="J12" s="4">
-        <f>G$2*(B12-G$3)</f>
+      <c r="J12" s="3">
+        <f t="shared" si="0"/>
         <v>1.1113000000011943</v>
       </c>
-      <c r="K12" s="3">
-        <f t="shared" si="1"/>
+      <c r="K12" s="2">
+        <f t="shared" si="8"/>
         <v>9.7522237764851236E-3</v>
       </c>
       <c r="L12">
         <v>-4.8399999999999999E-2</v>
       </c>
       <c r="M12">
-        <f>(C12-J12)^2</f>
+        <f t="shared" si="4"/>
         <v>7.290000006449234E-6</v>
       </c>
       <c r="N12">
+        <f t="shared" si="5"/>
+        <v>7.7159630350186997E-8</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="1"/>
+        <v>1.1108034062852583</v>
+      </c>
+      <c r="R12">
         <f t="shared" si="2"/>
-        <v>7.7159630350186997E-8</v>
-      </c>
-      <c r="O12">
-        <f>(E12-L12)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <f>U$2*(SIN(B12)-TAN(U$3)*COS(B12))</f>
-        <v>1.1108034062852583</v>
-      </c>
-      <c r="R12">
-        <f>(C12-Q12)^2</f>
         <v>4.8549992579156937E-6</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="B13">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <f t="shared" si="0"/>
         <v>0.17453292519943295</v>
       </c>
       <c r="C13">
@@ -6848,35 +6608,35 @@
       <c r="E13">
         <v>-4.4600000000000001E-2</v>
       </c>
-      <c r="J13" s="4">
-        <f>G$2*(B13-G$3)</f>
+      <c r="J13" s="3">
+        <f t="shared" si="0"/>
         <v>1.330622727273959</v>
       </c>
-      <c r="K13" s="3">
-        <f t="shared" si="1"/>
+      <c r="K13" s="2">
+        <f t="shared" si="8"/>
         <v>1.2105104896315132E-2</v>
       </c>
       <c r="L13">
         <v>-4.4600000000000001E-2</v>
       </c>
       <c r="M13">
-        <f>(C13-J13)^2</f>
+        <f t="shared" si="4"/>
         <v>6.112132438625546E-4</v>
       </c>
       <c r="N13">
+        <f t="shared" si="5"/>
+        <v>3.418619936663841E-8</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="1"/>
+        <v>1.3269171638736661</v>
+      </c>
+      <c r="R13">
         <f t="shared" si="2"/>
-        <v>3.418619936663841E-8</v>
-      </c>
-      <c r="O13">
-        <f>(E13-L13)^2</f>
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <f>U$2*(SIN(B13)-TAN(U$3)*COS(B13))</f>
-        <v>1.3269171638736661</v>
-      </c>
-      <c r="R13">
-        <f>(C13-Q13)^2</f>
         <v>4.4172117729253266E-4</v>
       </c>
     </row>
